--- a/DesignData/Original_Monster.xlsx
+++ b/DesignData/Original_Monster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unreal\Projects\Project_MMORPG\DesignData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D85BF7-D31A-4E17-B3AF-692F64A5BAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7CC9D0-0A01-4077-B8FF-025A6D728D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{1E70E408-E624-4B81-99D5-889082593FF6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1E70E408-E624-4B81-99D5-889082593FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="몬스터(5000~5999)" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>monster_name</t>
   </si>
@@ -157,14 +157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>monster_class</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLIENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"초급 슈퍼 미니언"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -174,42 +166,6 @@
   </si>
   <si>
     <t>"고급 슈퍼 미니언"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/MeleeMonster/BP_Beginner_MeleeMinion.BP_Beginner_MeleeMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/RangedMonster/BP_Beginner_RangedMinion.BP_Beginner_RangedMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/SuperMonster/BP_Beginner_SuperMinion.BP_Beginner_SuperMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/MeleeMonster/BP_Intermediate_MeleeMinion.BP_Intermediate_MeleeMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/RangedMonster/BP_Intermediate_RangedMinion.BP_Intermediate_RangedMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/SuperMonster/BP_Intermediate_SuperMinion.BP_Intermediate_SuperMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/MeleeMonster/BP_Expert_MeleeMinion.BP_Expert_MeleeMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/RangedMonster/BP_Expert_RangedMinion.BP_Expert_RangedMinion_C"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Blueprints/Creatures/Monster/SuperMonster/BP_Expert_SuperMinion.BP_Expert_SuperMinion_C"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -594,13 +550,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424A49E2-B413-473B-95D1-65DE3060862F}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -620,10 +576,10 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -632,22 +588,19 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="L1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="M1" t="s">
         <v>4</v>
       </c>
       <c r="N1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -690,11 +643,8 @@
       <c r="N2" t="s">
         <v>17</v>
       </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>5000</v>
       </c>
@@ -737,11 +687,8 @@
       <c r="N3">
         <v>1200</v>
       </c>
-      <c r="O3" t="s">
-        <v>42</v>
-      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>5001</v>
       </c>
@@ -784,11 +731,8 @@
       <c r="N4">
         <v>1200</v>
       </c>
-      <c r="O4" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>5002</v>
       </c>
@@ -796,7 +740,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -831,11 +775,8 @@
       <c r="N5">
         <v>1200</v>
       </c>
-      <c r="O5" t="s">
-        <v>44</v>
-      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5003</v>
       </c>
@@ -878,11 +819,8 @@
       <c r="N6">
         <v>1200</v>
       </c>
-      <c r="O6" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5004</v>
       </c>
@@ -925,11 +863,8 @@
       <c r="N7">
         <v>1200</v>
       </c>
-      <c r="O7" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>5005</v>
       </c>
@@ -937,7 +872,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -972,11 +907,8 @@
       <c r="N8">
         <v>1200</v>
       </c>
-      <c r="O8" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>5006</v>
       </c>
@@ -1019,11 +951,8 @@
       <c r="N9">
         <v>1200</v>
       </c>
-      <c r="O9" t="s">
-        <v>48</v>
-      </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>5007</v>
       </c>
@@ -1066,11 +995,8 @@
       <c r="N10">
         <v>1200</v>
       </c>
-      <c r="O10" t="s">
-        <v>49</v>
-      </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>5008</v>
       </c>
@@ -1078,7 +1004,7 @@
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
@@ -1112,9 +1038,6 @@
       </c>
       <c r="N11">
         <v>1200</v>
-      </c>
-      <c r="O11" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Original_Monster.xlsx
+++ b/DesignData/Original_Monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unreal\Projects\Project_MMORPG\DesignData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7CC9D0-0A01-4077-B8FF-025A6D728D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12E0A03-0812-4BE9-A8EF-F36ABEE9CA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1E70E408-E624-4B81-99D5-889082593FF6}"/>
   </bookViews>
@@ -661,7 +661,7 @@
         <v>200</v>
       </c>
       <c r="F3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>300</v>
